--- a/Use-Case_Description--Upload_Audio_Files.xlsx
+++ b/Use-Case_Description--Upload_Audio_Files.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thoma\Documents\GitHub\Audio_Analyzer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE00DAE7-AD88-4A4F-9714-E99BA3DDAEE3}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88A3045C-C1DE-4ADB-9D4F-CDB425F1DB41}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="70" yWindow="60" windowWidth="19120" windowHeight="20670" xr2:uid="{F029340B-59BC-4187-9937-02EC323D7EB9}"/>
+    <workbookView xWindow="100" yWindow="80" windowWidth="19120" windowHeight="20670" xr2:uid="{F029340B-59BC-4187-9937-02EC323D7EB9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -121,9 +121,6 @@
   </si>
   <si>
     <t>Created: 01/23/21 by Tom Lever</t>
-  </si>
-  <si>
-    <t>Updated: 01/23/21 by Tom Lever</t>
   </si>
   <si>
     <t>Constraints that must be met for the use case to be taken by the solution developer and used to create a workflow.
@@ -277,6 +274,9 @@
   </si>
   <si>
     <t>Upload Audio Files</t>
+  </si>
+  <si>
+    <t>Updated: 01/26/21 by Tom Lever</t>
   </si>
 </sst>
 </file>
@@ -731,7 +731,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -741,18 +741,18 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -760,7 +760,7 @@
         <v>0</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>2</v>
@@ -782,10 +782,10 @@
         <v>24</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -793,7 +793,7 @@
         <v>4</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>8</v>
@@ -804,7 +804,7 @@
         <v>5</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>9</v>
@@ -818,7 +818,7 @@
         <v>23</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="29" x14ac:dyDescent="0.35">
@@ -826,10 +826,10 @@
         <v>7</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
@@ -848,10 +848,10 @@
         <v>25</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
@@ -859,12 +859,12 @@
         <v>26</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
       <c r="B20" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
@@ -894,7 +894,7 @@
         <v>13</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>19</v>
@@ -905,7 +905,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C24" s="11" t="s">
         <v>20</v>

--- a/Use-Case_Description--Upload_Audio_Files.xlsx
+++ b/Use-Case_Description--Upload_Audio_Files.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thoma\Documents\GitHub\Audio_Analyzer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88A3045C-C1DE-4ADB-9D4F-CDB425F1DB41}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5399764B-B252-437E-A3C3-5CF6CF629819}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="100" yWindow="80" windowWidth="19120" windowHeight="20670" xr2:uid="{F029340B-59BC-4187-9937-02EC323D7EB9}"/>
+    <workbookView xWindow="19180" yWindow="0" windowWidth="19060" windowHeight="20670" xr2:uid="{F029340B-59BC-4187-9937-02EC323D7EB9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -163,28 +163,19 @@
     <t>The Uploader is presented with whether or not each upload succeeded.</t>
   </si>
   <si>
+    <t>Upload Audio Files</t>
+  </si>
+  <si>
+    <t>Updated: 01/26/21 by Tom Lever</t>
+  </si>
+  <si>
     <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Alternate Flow 1:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-5.1. The Uploader abandons uploading an audio file.
-5.2. The system provides a status of "abandoned upload" to the Uploader for that audio file.
+      <t xml:space="preserve">1. An Uploader signals desire to upload one or more audio files.
+2. The system provides to the Uploader a mechanism to upload the audio files.
+3. The Uploader specifies the audio file(s) to be uploaded.
+4. The Uploader signals that the specified audio file(s) should be uploaded by the system.
+5. The system uploads the audio file(s).
+6. The system provides to the Uploader an upload status for each audio file in the group of specified audio files.
 </t>
     </r>
     <r>
@@ -196,8 +187,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>This use case terminates after some combination of the main flow and the alternate flows
-complete for each audio file.</t>
+      <t>This use case terminates.</t>
     </r>
   </si>
   <si>
@@ -222,7 +212,7 @@
       </rPr>
       <t xml:space="preserve">
 5.1. The system fails to upload an audio file.
-5.2. The system provides a status of "failed upload" to the Uploader for that audio file.
+5.2. The status of the audio file whose upload failed becomes "failed upload".
 </t>
     </r>
     <r>
@@ -234,18 +224,33 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>This use case terminates after some combination of the main flow and the alternate flows
-complete for each audio file.</t>
+      <t>This use case continues at step 5 of the main flow.</t>
     </r>
   </si>
   <si>
     <r>
-      <t xml:space="preserve">1. An Uploader signals desire to upload one or more audio files.
-2. The system provides to the Uploader a mechanism to upload the audio files.
-3. The Uploader specifies the audio file(s) to be uploaded.
-4. The Uploader signals that each audio file should be uploaded by the system.
-5. The system uploads the audio file(s).
-6. The system provides a status of "successful upload" to the Uploader for each audio file uploaded successfully.
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Alternate Flow 1:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+5.1. The Uploader signals that uploading of an audio file in the group of audio files being uploaded should be abandoned.
+5.2. The system removes the abandoned audio file from the group of audio files being uploaded.
+5.3. The status of the audio file that was abandoned becomes "abandoned upload".
 </t>
     </r>
     <r>
@@ -257,26 +262,18 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>This use case terminates.</t>
+      <t>This use case continues at step 5 of the main flow.</t>
     </r>
   </si>
   <si>
     <t>Uploader: (1) Signal desire to upload and submit one or more audio files
 Uploader: (3) Specify audio file(s)
 Uploader: (4) Signal that each audio file should be uploaded by the system
-Uploader: (AF1-5.1) Signal to abandon audio file</t>
+Uploader: (AF1-5.1) Signal to abandon uploading of audio file</t>
   </si>
   <si>
     <t>(2) Mechanism to upload one or more audio files
-(6) Status of "successful upload"
-(AF1-5.2) Status of "abandoned upload"
-(AF2-5.2) Status of "failed upload"</t>
-  </si>
-  <si>
-    <t>Upload Audio Files</t>
-  </si>
-  <si>
-    <t>Updated: 01/26/21 by Tom Lever</t>
+(6) Status of "successful upload" for all uploaded audio files, "abandoned upload" for all audio files whose status were set to "abandoned upload", and "failed upload" for all audio files whose status were set to "failed upload".</t>
   </si>
 </sst>
 </file>
@@ -718,7 +715,7 @@
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="36" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="93.08984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="93.54296875" style="4" customWidth="1"/>
     <col min="3" max="3" width="110.453125" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="99.26953125" style="4" customWidth="1"/>
     <col min="5" max="16384" width="8.81640625" style="4"/>
@@ -731,7 +728,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -741,7 +738,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -760,7 +757,7 @@
         <v>0</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>2</v>
@@ -854,17 +851,17 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" ht="87" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>26</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="B20" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
@@ -894,7 +891,7 @@
         <v>13</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>19</v>
@@ -905,7 +902,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C24" s="11" t="s">
         <v>20</v>

--- a/Use-Case_Description--Upload_Audio_Files.xlsx
+++ b/Use-Case_Description--Upload_Audio_Files.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thoma\Documents\GitHub\Audio_Analyzer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5399764B-B252-437E-A3C3-5CF6CF629819}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29E6A2D5-9466-4125-A5D6-CD547DB59BF7}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19180" yWindow="0" windowWidth="19060" windowHeight="20670" xr2:uid="{F029340B-59BC-4187-9937-02EC323D7EB9}"/>
+    <workbookView xWindow="19200" yWindow="100" windowWidth="19060" windowHeight="20670" xr2:uid="{F029340B-59BC-4187-9937-02EC323D7EB9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -266,14 +266,14 @@
     </r>
   </si>
   <si>
-    <t>Uploader: (1) Signal desire to upload and submit one or more audio files
+    <t>(2) Mechanism to upload one or more audio files
+(6) Status of "successful upload" for all uploaded audio files, "abandoned upload" for all audio files whose status were set to "abandoned upload", and "failed upload" for all audio files whose status were set to "failed upload".</t>
+  </si>
+  <si>
+    <t>Uploader: (1) Signal of desire to upload and submit one or more audio files
 Uploader: (3) Specify audio file(s)
 Uploader: (4) Signal that each audio file should be uploaded by the system
 Uploader: (AF1-5.1) Signal to abandon uploading of audio file</t>
-  </si>
-  <si>
-    <t>(2) Mechanism to upload one or more audio files
-(6) Status of "successful upload" for all uploaded audio files, "abandoned upload" for all audio files whose status were set to "abandoned upload", and "failed upload" for all audio files whose status were set to "failed upload".</t>
   </si>
 </sst>
 </file>
@@ -891,7 +891,7 @@
         <v>13</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>19</v>
@@ -902,7 +902,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C24" s="11" t="s">
         <v>20</v>
